--- a/data/trans_orig/IQ23_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ23_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35034</t>
+          <t>35161</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44580</t>
+          <t>44813</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44799</t>
+          <t>45137</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54484</t>
+          <t>54738</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83018</t>
+          <t>83254</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97048</t>
+          <t>96744</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17534</t>
+          <t>17407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15418</t>
+          <t>15080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>16041</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29767</t>
+          <t>29531</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50737</t>
+          <t>50493</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66831</t>
+          <t>66527</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65567</t>
+          <t>65086</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81017</t>
+          <t>81200</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>121647</t>
+          <t>120228</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143995</t>
+          <t>143487</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,22%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34731</t>
+          <t>35035</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50825</t>
+          <t>51069</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27740</t>
+          <t>27557</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43190</t>
+          <t>43671</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>66324</t>
+          <t>66832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>88672</t>
+          <t>90091</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,84%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50108</t>
+          <t>50209</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60453</t>
+          <t>60427</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49500</t>
+          <t>49551</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60172</t>
+          <t>59598</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103255</t>
+          <t>103702</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118109</t>
+          <t>118569</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,97%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7170</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>17388</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10155</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20827</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19815</t>
+          <t>19355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34669</t>
+          <t>34222</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57284</t>
+          <t>57528</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67172</t>
+          <t>67442</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57945</t>
+          <t>58474</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69894</t>
+          <t>69793</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119724</t>
+          <t>119675</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135269</t>
+          <t>134643</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17577</t>
+          <t>17333</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21166</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18703</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34248</t>
+          <t>34297</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25591</t>
+          <t>25325</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34672</t>
+          <t>34933</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23989</t>
+          <t>24383</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34448</t>
+          <t>34452</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52793</t>
+          <t>52548</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66959</t>
+          <t>66362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>76,55%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16261</t>
+          <t>16527</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10391</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20854</t>
+          <t>20460</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19736</t>
+          <t>20333</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33902</t>
+          <t>34147</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,39%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41521</t>
+          <t>41665</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50708</t>
+          <t>50596</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45134</t>
+          <t>44847</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53829</t>
+          <t>53740</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89761</t>
+          <t>90850</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>102425</t>
+          <t>102987</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,94%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14534</t>
+          <t>14390</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14598</t>
+          <t>14885</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26026</t>
+          <t>24937</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91701</t>
+          <t>92469</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>107432</t>
+          <t>107967</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>92636</t>
+          <t>93363</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>109518</t>
+          <t>109969</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>190119</t>
+          <t>191290</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>213375</t>
+          <t>214335</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>81,1%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21190</t>
+          <t>20655</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36921</t>
+          <t>36153</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26137</t>
+          <t>25686</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43019</t>
+          <t>42292</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>50902</t>
+          <t>49942</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>74158</t>
+          <t>72987</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>90377</t>
+          <t>90570</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>108602</t>
+          <t>109160</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>97213</t>
+          <t>97659</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>116079</t>
+          <t>115890</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>194327</t>
+          <t>193033</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>220429</t>
+          <t>218653</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>69,89%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43422</t>
+          <t>42864</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>61647</t>
+          <t>61454</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>44758</t>
+          <t>44947</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>63624</t>
+          <t>63178</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>92432</t>
+          <t>94208</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>118534</t>
+          <t>119828</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>477467</t>
+          <t>478826</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>514381</t>
+          <t>515681</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>511759</t>
+          <t>513998</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>550048</t>
+          <t>550329</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1003068</t>
+          <t>1002908</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1055854</t>
+          <t>1055340</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,67%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>160760</t>
+          <t>159460</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>197674</t>
+          <t>196315</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>169431</t>
+          <t>169150</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>207720</t>
+          <t>205481</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>338766</t>
+          <t>339280</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>391552</t>
+          <t>391712</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24802</t>
+          <t>23712</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37109</t>
+          <t>36379</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32216</t>
+          <t>31858</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45315</t>
+          <t>45080</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60698</t>
+          <t>61421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78700</t>
+          <t>79510</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>65,05%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>21048</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32625</t>
+          <t>33715</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19494</t>
+          <t>19729</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32593</t>
+          <t>32951</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43536</t>
+          <t>42726</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61538</t>
+          <t>60815</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>49,75%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63530</t>
+          <t>63641</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79719</t>
+          <t>79447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73879</t>
+          <t>73504</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89119</t>
+          <t>88764</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>143661</t>
+          <t>142680</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>163982</t>
+          <t>163459</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,96%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24319</t>
+          <t>24591</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40508</t>
+          <t>40397</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>22395</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37280</t>
+          <t>37655</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51215</t>
+          <t>51738</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71536</t>
+          <t>72517</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51498</t>
+          <t>50468</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61134</t>
+          <t>61151</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48421</t>
+          <t>49220</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60215</t>
+          <t>60404</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>104632</t>
+          <t>104674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119473</t>
+          <t>118630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,56%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15893</t>
+          <t>16923</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11039</t>
+          <t>10850</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22833</t>
+          <t>22034</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19172</t>
+          <t>20015</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34013</t>
+          <t>33971</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49475</t>
+          <t>49706</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62340</t>
+          <t>62508</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53227</t>
+          <t>53150</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66293</t>
+          <t>66097</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107214</t>
+          <t>106915</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126263</t>
+          <t>125533</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>78,79%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15421</t>
+          <t>15253</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28286</t>
+          <t>28055</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15273</t>
+          <t>15469</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28339</t>
+          <t>28416</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33064</t>
+          <t>33794</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52113</t>
+          <t>52412</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19467</t>
+          <t>18868</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30898</t>
+          <t>30304</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22266</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33429</t>
+          <t>33497</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45337</t>
+          <t>44428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60881</t>
+          <t>60514</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,75%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>13597</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24434</t>
+          <t>25033</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13323</t>
+          <t>13255</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24486</t>
+          <t>24535</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29772</t>
+          <t>30139</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45316</t>
+          <t>46225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,99%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41503</t>
+          <t>42204</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50693</t>
+          <t>50807</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36386</t>
+          <t>36154</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48306</t>
+          <t>47907</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80966</t>
+          <t>81271</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>96792</t>
+          <t>96410</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>82,95%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>12338</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23859</t>
+          <t>24091</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19438</t>
+          <t>19820</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35264</t>
+          <t>34959</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>98370</t>
+          <t>98615</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>114964</t>
+          <t>114896</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98425</t>
+          <t>97984</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116182</t>
+          <t>115752</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>201326</t>
+          <t>202111</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>226807</t>
+          <t>226590</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,84%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23754</t>
+          <t>23822</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40348</t>
+          <t>40103</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>29319</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>46646</t>
+          <t>47087</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>56982</t>
+          <t>57199</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>82463</t>
+          <t>81678</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>105898</t>
+          <t>105283</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>124676</t>
+          <t>124775</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>112264</t>
+          <t>113898</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>132443</t>
+          <t>131903</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>224333</t>
+          <t>224533</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>252012</t>
+          <t>251132</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>40032</t>
+          <t>39933</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>58810</t>
+          <t>59425</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>38872</t>
+          <t>39412</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59051</t>
+          <t>57417</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>84011</t>
+          <t>84891</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>111690</t>
+          <t>111490</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>490168</t>
+          <t>491483</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>529356</t>
+          <t>531483</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>517703</t>
+          <t>516931</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>559539</t>
+          <t>557348</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1022475</t>
+          <t>1019954</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1079630</t>
+          <t>1078025</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,73%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>180573</t>
+          <t>178446</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>219761</t>
+          <t>218446</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>192632</t>
+          <t>194823</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>234468</t>
+          <t>235240</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>382470</t>
+          <t>384075</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>439625</t>
+          <t>442146</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,24%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28476</t>
+          <t>28386</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39801</t>
+          <t>40103</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30152</t>
+          <t>31035</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43207</t>
+          <t>44568</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62654</t>
+          <t>61367</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80831</t>
+          <t>80087</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>65,73%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17570</t>
+          <t>17268</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28895</t>
+          <t>28985</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21255</t>
+          <t>19894</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34310</t>
+          <t>33427</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41002</t>
+          <t>41746</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59179</t>
+          <t>60466</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>49,63%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48075</t>
+          <t>47748</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64829</t>
+          <t>64705</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54411</t>
+          <t>55242</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72387</t>
+          <t>72242</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108205</t>
+          <t>107586</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>132253</t>
+          <t>132057</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,98%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37947</t>
+          <t>38071</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54701</t>
+          <t>55028</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37896</t>
+          <t>38041</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55872</t>
+          <t>55041</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>80806</t>
+          <t>81002</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>104854</t>
+          <t>105473</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,5%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29468</t>
+          <t>28550</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43589</t>
+          <t>42852</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33593</t>
+          <t>33292</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46534</t>
+          <t>46284</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67188</t>
+          <t>66748</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86570</t>
+          <t>85806</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>63,74%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22516</t>
+          <t>23253</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36637</t>
+          <t>37555</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21983</t>
+          <t>22233</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34924</t>
+          <t>35225</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48052</t>
+          <t>48816</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67434</t>
+          <t>67874</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,42%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48217</t>
+          <t>48091</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61058</t>
+          <t>61180</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45984</t>
+          <t>45855</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60785</t>
+          <t>60160</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98692</t>
+          <t>98173</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118391</t>
+          <t>116957</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>73,96%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15903</t>
+          <t>15781</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28744</t>
+          <t>28870</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20399</t>
+          <t>21024</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35200</t>
+          <t>35329</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39754</t>
+          <t>41188</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>59453</t>
+          <t>59972</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32794</t>
+          <t>32854</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40283</t>
+          <t>40351</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34485</t>
+          <t>33810</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42383</t>
+          <t>42428</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69553</t>
+          <t>69581</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80813</t>
+          <t>81055</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10644</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>12540</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8975</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20235</t>
+          <t>20207</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31648</t>
+          <t>31475</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42535</t>
+          <t>42580</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35337</t>
+          <t>34615</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46537</t>
+          <t>46693</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70369</t>
+          <t>69185</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>86925</t>
+          <t>86472</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,2%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11738</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22625</t>
+          <t>22798</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>11046</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22402</t>
+          <t>23124</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25087</t>
+          <t>25540</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41643</t>
+          <t>42827</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>88304</t>
+          <t>87947</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105387</t>
+          <t>105068</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>85425</t>
+          <t>84801</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>103726</t>
+          <t>103669</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>179432</t>
+          <t>178835</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>203440</t>
+          <t>204779</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,76%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31987</t>
+          <t>32306</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49070</t>
+          <t>49427</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>40346</t>
+          <t>40403</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>58647</t>
+          <t>59271</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>78006</t>
+          <t>76667</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>102014</t>
+          <t>102611</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>117701</t>
+          <t>117401</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>133691</t>
+          <t>133357</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>113636</t>
+          <t>115535</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>132283</t>
+          <t>132575</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>237850</t>
+          <t>238045</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>262199</t>
+          <t>262180</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>27264</t>
+          <t>27598</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>43254</t>
+          <t>43554</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33352</t>
+          <t>33060</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51999</t>
+          <t>50100</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>64391</t>
+          <t>64410</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>88740</t>
+          <t>88545</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>461446</t>
+          <t>458336</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>500446</t>
+          <t>497620</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>474082</t>
+          <t>472693</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>515200</t>
+          <t>515355</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>939878</t>
+          <t>945678</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>999255</t>
+          <t>1002204</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>198807</t>
+          <t>201633</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>237807</t>
+          <t>240917</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>223042</t>
+          <t>222887</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>264160</t>
+          <t>265549</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>438240</t>
+          <t>435291</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>497617</t>
+          <t>491817</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50887</t>
+          <t>51377</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63523</t>
+          <t>64099</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>49116</t>
+          <t>49643</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63142</t>
+          <t>64077</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105104</t>
+          <t>104673</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125363</t>
+          <t>123597</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>80,97%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>9183</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22395</t>
+          <t>21905</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16224</t>
+          <t>15289</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30250</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27285</t>
+          <t>29051</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47544</t>
+          <t>47975</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89161</t>
+          <t>88372</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>114062</t>
+          <t>112654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75754</t>
+          <t>75201</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96337</t>
+          <t>96552</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>170718</t>
+          <t>170104</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>208312</t>
+          <t>206366</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,5%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11945</t>
+          <t>13353</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36846</t>
+          <t>37635</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51446</t>
+          <t>51999</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>44895</t>
+          <t>46841</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>82489</t>
+          <t>83103</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26792</t>
+          <t>26967</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38459</t>
+          <t>38900</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34867</t>
+          <t>33836</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47210</t>
+          <t>47094</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65507</t>
+          <t>64935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82387</t>
+          <t>82546</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19809</t>
+          <t>19368</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31476</t>
+          <t>31301</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19953</t>
+          <t>20069</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32296</t>
+          <t>33327</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43044</t>
+          <t>42885</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59924</t>
+          <t>60496</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44409</t>
+          <t>44837</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56022</t>
+          <t>55966</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49409</t>
+          <t>48614</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66195</t>
+          <t>66401</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98514</t>
+          <t>97963</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118881</t>
+          <t>119367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,16%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9272</t>
+          <t>9328</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>20457</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10339</t>
+          <t>10133</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27125</t>
+          <t>27920</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22946</t>
+          <t>22460</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43313</t>
+          <t>43864</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22120</t>
+          <t>22266</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29121</t>
+          <t>29065</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30797</t>
+          <t>30355</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37250</t>
+          <t>37445</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55212</t>
+          <t>55007</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64581</t>
+          <t>65033</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,44%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12393</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20020</t>
+          <t>20225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23617</t>
+          <t>23379</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33553</t>
+          <t>33233</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23585</t>
+          <t>23741</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35875</t>
+          <t>35865</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49498</t>
+          <t>50428</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65945</t>
+          <t>65896</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,38%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12614</t>
+          <t>12934</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22550</t>
+          <t>22788</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20311</t>
+          <t>20321</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32601</t>
+          <t>32445</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36408</t>
+          <t>36457</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>52855</t>
+          <t>51925</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>50,73%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53519</t>
+          <t>52912</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73273</t>
+          <t>72945</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>73386</t>
+          <t>74511</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100801</t>
+          <t>100606</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>133156</t>
+          <t>135282</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>168077</t>
+          <t>167804</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,82%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>51235</t>
+          <t>51563</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>70989</t>
+          <t>71596</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>55211</t>
+          <t>55406</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>82626</t>
+          <t>81501</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>112443</t>
+          <t>112716</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>147364</t>
+          <t>145238</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>51,77%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>102249</t>
+          <t>101404</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>116053</t>
+          <t>115708</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>127760</t>
+          <t>128077</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>142532</t>
+          <t>142283</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>234042</t>
+          <t>234439</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>254093</t>
+          <t>254372</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,2%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15566</t>
+          <t>15911</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29370</t>
+          <t>30215</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14263</t>
+          <t>14512</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29035</t>
+          <t>28718</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34321</t>
+          <t>34042</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>54372</t>
+          <t>53975</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>447035</t>
+          <t>447861</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>496594</t>
+          <t>495758</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>503401</t>
+          <t>504217</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>552053</t>
+          <t>554632</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>963471</t>
+          <t>967512</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1034488</t>
+          <t>1032773</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>163065</t>
+          <t>163901</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>212624</t>
+          <t>211798</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>207922</t>
+          <t>205343</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>256574</t>
+          <t>255758</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>385146</t>
+          <t>386861</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>456163</t>
+          <t>452122</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
